--- a/backend/local_storage/attendance.xlsx
+++ b/backend/local_storage/attendance.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,8 +487,41 @@
           <t>2026-08-13 12:00:27</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-08-13 22:00:27</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>RV001</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-08-14 11:03:26</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
         <is>
           <t>Present</t>
         </is>

--- a/backend/local_storage/attendance.xlsx
+++ b/backend/local_storage/attendance.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,8 +520,41 @@
           <t>2026-08-14 11:03:26</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-08-14 21:03:26</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>RV001</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:32:13</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
         <is>
           <t>Present</t>
         </is>
